--- a/templates/hssk_template.xlsx
+++ b/templates/hssk_template.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Hướng dẫn" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dữ liệu'!$A$1:$Q$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Dữ liệu'!$A$1:$AV$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <sz val="14"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C55A11"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00833C00"/>
       </patternFill>
     </fill>
     <fill>
@@ -74,12 +79,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -184,6 +192,7 @@
       <text>
         <t>Trường API: examinationDate
 Kiểu: Ngày dd/mm/yyyy
+(Bắt buộc)
 Ngày khám. Bỏ trống giờ sẽ dùng giờ mặc định trong cấu hình.</t>
       </text>
     </comment>
@@ -191,101 +200,325 @@
       <text>
         <t>Trường API: finishExaminationDate
 Kiểu: Ngày dd/mm/yyyy
+(Bắt buộc)
 Ngày/giờ kết thúc khám. Phải sau 'Ngày khám'.</t>
       </text>
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: typeOfExamination
+Kiểu: Số nguyên
+(Bắt buộc)
+Mã loại khám. Mặc định: 100 (khám ngoại trú).</t>
+      </text>
+    </comment>
+    <comment ref="E1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: reasonCode
+Kiểu: Số nguyên
+(Bắt buộc)
+Mã lý do khám. Mặc định: 93.</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: reasonsMedicalexamination
+Kiểu: Chữ
+Lý do khám, ví dụ 'Khám sức khoẻ'.</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: symptoms
+Kiểu: Chữ
+Triệu chứng, ví dụ 'Không'.</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: bodySkinDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: bodyOtherDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: heartDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: respiratoryDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="L1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: digestDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="M1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: urologyDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: nerveDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: osteoarthritisDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: endocrineDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: bloodDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: surgeryDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: maternityDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'. Điền N/A nếu không áp dụng.</t>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: earNoseThroatDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: toothDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: eyeDesc
+Kiểu: Chữ
+Mô tả khám mắt (phân biệt với thị lực số). Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="W1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: dermatologyDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="X1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: nutritionDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="Y1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: motionDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="Z1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: physicalDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="AA1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: organsOtherDesc
+Kiểu: Chữ
+Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: diagnosesDischarge
+Kiểu: Chữ
+(Bắt buộc)
+Chẩn đoán ra viện, ví dụ '0000 - Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="AC1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: diagnosesDischargeList
+Kiểu: Danh sách (mỗi mục một dòng, hoặc phân tách bằng ;)
+Danh sách chẩn đoán. Để trống sẽ tự sao chép từ cột 'Chẩn đoán'. Nhiều mục: mỗi mục một dòng hoặc phân tách bằng ;</t>
+      </text>
+    </comment>
+    <comment ref="AD1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: noteDisease
+Kiểu: Chữ
+Ghi chú bệnh lý, ví dụ 'Không'.</t>
+      </text>
+    </comment>
+    <comment ref="AE1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: treatmentDirection
+Kiểu: Chữ
+Hướng điều trị. Để trống = 'Bình thường'.</t>
+      </text>
+    </comment>
+    <comment ref="AF1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: treatmentResultId
+Kiểu: Số nguyên
+(Bắt buộc)
+Mã kết quả điều trị (số nguyên). Mặc định: 3.</t>
+      </text>
+    </comment>
+    <comment ref="AG1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: dischargeStatusId
+Kiểu: Số nguyên
+(Bắt buộc)
+Mã tình trạng ra viện (số nguyên). Mặc định: 1.</t>
+      </text>
+    </comment>
+    <comment ref="AH1" authorId="0" shapeId="0">
+      <text>
+        <t>Trường API: doctorName
+Kiểu: Chữ
+(Bắt buộc)
+Tên bác sĩ. Để trống dùng giá trị mặc định trong cấu hình.</t>
+      </text>
+    </comment>
+    <comment ref="AI1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: pulse
 Kiểu: Số nguyên
 Mạch (lần/phút), ví dụ 80.</t>
       </text>
     </comment>
-    <comment ref="E1" authorId="0" shapeId="0">
+    <comment ref="AJ1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: temperature
 Kiểu: Số thập phân
 Nhiệt độ °C, ví dụ 36.8.</t>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0">
+    <comment ref="AK1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: bloodPressureMax
 Kiểu: Số nguyên
 Huyết áp tối đa (tâm thu), ví dụ 110.</t>
       </text>
     </comment>
-    <comment ref="G1" authorId="0" shapeId="0">
+    <comment ref="AL1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: bloodPressureMin
 Kiểu: Số nguyên
 Huyết áp tối thiểu (tâm trương), ví dụ 70.</t>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0">
+    <comment ref="AM1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: breath
 Kiểu: Số nguyên
 Nhịp thở (lần/phút), ví dụ 20.</t>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0">
+    <comment ref="AN1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: weight
 Kiểu: Số
 Cân nặng (kg).</t>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0">
+    <comment ref="AO1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: height
 Kiểu: Số
 Chiều cao (cm).</t>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0">
+    <comment ref="AP1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: bmi
 Kiểu: Số
 ĐỂ TRỐNG để tự tính từ cân nặng &amp; chiều cao.</t>
       </text>
     </comment>
-    <comment ref="L1" authorId="0" shapeId="0">
+    <comment ref="AQ1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: waistCircumference
 Kiểu: Số nguyên
 Vòng bụng (cm).</t>
       </text>
     </comment>
-    <comment ref="M1" authorId="0" shapeId="0">
+    <comment ref="AR1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: chestCircumference
 Kiểu: Số nguyên
 Vòng ngực (cm).</t>
       </text>
     </comment>
-    <comment ref="N1" authorId="0" shapeId="0">
+    <comment ref="AS1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: leftEyeGlasses
 Kiểu: Số nguyên
 Thị lực mắt trái (có kính).</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="AT1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: leftEyeNoGlasses
 Kiểu: Số nguyên
 Thị lực mắt trái (không kính).</t>
       </text>
     </comment>
-    <comment ref="P1" authorId="0" shapeId="0">
+    <comment ref="AU1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: rightEyeGlasses
 Kiểu: Số nguyên
 Thị lực mắt phải (có kính).</t>
       </text>
     </comment>
-    <comment ref="Q1" authorId="0" shapeId="0">
+    <comment ref="AV1" authorId="0" shapeId="0">
       <text>
         <t>Trường API: rightEyeNoGlasses
 Kiểu: Số nguyên
@@ -585,26 +818,57 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:AV3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="13" customWidth="1" min="13" max="13"/>
-    <col width="19" customWidth="1" min="14" max="14"/>
-    <col width="25" customWidth="1" min="15" max="15"/>
-    <col width="19" customWidth="1" min="16" max="16"/>
-    <col width="25" customWidth="1" min="17" max="17"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="19" customWidth="1" min="13" max="13"/>
+    <col width="24" customWidth="1" min="14" max="14"/>
+    <col width="17" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="14" customWidth="1" min="18" max="18"/>
+    <col width="16" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="16" customWidth="1" min="21" max="21"/>
+    <col width="12" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="30" customWidth="1" min="26" max="26"/>
+    <col width="16" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="17" customWidth="1" min="29" max="29"/>
+    <col width="17" customWidth="1" min="30" max="30"/>
+    <col width="19" customWidth="1" min="31" max="31"/>
+    <col width="19" customWidth="1" min="32" max="32"/>
+    <col width="25" customWidth="1" min="33" max="33"/>
+    <col width="12" customWidth="1" min="34" max="34"/>
+    <col width="12" customWidth="1" min="35" max="35"/>
+    <col width="12" customWidth="1" min="36" max="36"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col width="12" customWidth="1" min="40" max="40"/>
+    <col width="13" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="42" max="42"/>
+    <col width="13" customWidth="1" min="43" max="43"/>
+    <col width="13" customWidth="1" min="44" max="44"/>
+    <col width="19" customWidth="1" min="45" max="45"/>
+    <col width="25" customWidth="1" min="46" max="46"/>
+    <col width="19" customWidth="1" min="47" max="47"/>
+    <col width="25" customWidth="1" min="48" max="48"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -625,183 +889,632 @@
       </c>
       <c r="D1" s="2" t="inlineStr">
         <is>
+          <t>Mã hình thức khám</t>
+        </is>
+      </c>
+      <c r="E1" s="2" t="inlineStr">
+        <is>
+          <t>Mã đối tượng khám</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Lý do khám</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Bệnh sử</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Da niêm mạc</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Toàn thân khác</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Tim mạch</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Hô hấp</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Tiêu hoá</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Thận, tiết niệu</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Tâm thần - Thần kinh</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Cơ xương khớp</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>Nội tiết</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>Bệnh máu</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>Ngoại khoa</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>Sản phụ khoa</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>Tai mũi họng</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>Răng hàm mặt</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Mắt</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Da liễu</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Dinh dưỡng</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Vận động</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Đánh giá phát triển thể chất</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Cơ quan khác</t>
+        </is>
+      </c>
+      <c r="AB1" s="2" t="inlineStr">
+        <is>
+          <t>Chẩn đoán</t>
+        </is>
+      </c>
+      <c r="AC1" s="3" t="inlineStr">
+        <is>
+          <t>Bệnh kèm theo</t>
+        </is>
+      </c>
+      <c r="AD1" s="3" t="inlineStr">
+        <is>
+          <t>Bệnh theo dõi</t>
+        </is>
+      </c>
+      <c r="AE1" s="3" t="inlineStr">
+        <is>
+          <t>Tư vấn điều trị</t>
+        </is>
+      </c>
+      <c r="AF1" s="2" t="inlineStr">
+        <is>
+          <t>Mã kết quả khám</t>
+        </is>
+      </c>
+      <c r="AG1" s="2" t="inlineStr">
+        <is>
+          <t>Mã tình trạng ra viện</t>
+        </is>
+      </c>
+      <c r="AH1" s="2" t="inlineStr">
+        <is>
+          <t>Bác sĩ</t>
+        </is>
+      </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
           <t>Mạch</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="AJ1" s="3" t="inlineStr">
         <is>
           <t>Nhiệt độ</t>
         </is>
       </c>
-      <c r="F1" s="2" t="inlineStr">
+      <c r="AK1" s="3" t="inlineStr">
         <is>
           <t>HA tối đa</t>
         </is>
       </c>
-      <c r="G1" s="2" t="inlineStr">
+      <c r="AL1" s="3" t="inlineStr">
         <is>
           <t>HA tối thiểu</t>
         </is>
       </c>
-      <c r="H1" s="2" t="inlineStr">
+      <c r="AM1" s="3" t="inlineStr">
         <is>
           <t>Nhịp thở</t>
         </is>
       </c>
-      <c r="I1" s="2" t="inlineStr">
+      <c r="AN1" s="3" t="inlineStr">
         <is>
           <t>Cân nặng</t>
         </is>
       </c>
-      <c r="J1" s="2" t="inlineStr">
+      <c r="AO1" s="3" t="inlineStr">
         <is>
           <t>Chiều cao</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="AP1" s="3" t="inlineStr">
         <is>
           <t>BMI</t>
         </is>
       </c>
-      <c r="L1" s="2" t="inlineStr">
+      <c r="AQ1" s="3" t="inlineStr">
         <is>
           <t>Vòng bụng</t>
         </is>
       </c>
-      <c r="M1" s="2" t="inlineStr">
+      <c r="AR1" s="3" t="inlineStr">
         <is>
           <t>Vòng ngực</t>
         </is>
       </c>
-      <c r="N1" s="2" t="inlineStr">
+      <c r="AS1" s="3" t="inlineStr">
         <is>
           <t>Mắt trái (kính)</t>
         </is>
       </c>
-      <c r="O1" s="2" t="inlineStr">
+      <c r="AT1" s="3" t="inlineStr">
         <is>
           <t>Mắt trái (không kính)</t>
         </is>
       </c>
-      <c r="P1" s="2" t="inlineStr">
+      <c r="AU1" s="3" t="inlineStr">
         <is>
           <t>Mắt phải (kính)</t>
         </is>
       </c>
-      <c r="Q1" s="2" t="inlineStr">
+      <c r="AV1" s="3" t="inlineStr">
         <is>
           <t>Mắt phải (không kính)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>027148003240</t>
         </is>
       </c>
-      <c r="B2" s="4" t="n">
+      <c r="B2" s="5" t="n">
         <v>46190.29166666666</v>
       </c>
-      <c r="C2" s="4" t="n">
+      <c r="C2" s="5" t="n">
         <v>46190.35416666666</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="D2" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F2" s="4" t="inlineStr">
+        <is>
+          <t>Khám sức khoẻ</t>
+        </is>
+      </c>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="P2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="Q2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="R2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="S2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="T2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="U2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="V2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="W2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="X2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="Y2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="Z2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="AA2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="AB2" s="4" t="inlineStr">
+        <is>
+          <t>0000 - Bình thường</t>
+        </is>
+      </c>
+      <c r="AC2" s="4" t="inlineStr">
+        <is>
+          <t>0000 - Bình thường</t>
+        </is>
+      </c>
+      <c r="AD2" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="AE2" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="AF2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hoa</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="AJ2" s="4" t="n">
         <v>36.8</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="AK2" s="4" t="n">
         <v>110</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="AL2" s="4" t="n">
         <v>70</v>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="AM2" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="AN2" s="4" t="n">
         <v>18</v>
       </c>
-      <c r="J2" s="3" t="n">
+      <c r="AO2" s="4" t="n">
         <v>140</v>
       </c>
-      <c r="K2" s="3" t="n"/>
-      <c r="L2" s="3" t="n">
+      <c r="AP2" s="4" t="n"/>
+      <c r="AQ2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="M2" s="3" t="n">
+      <c r="AR2" s="4" t="n">
         <v>60</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="AS2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O2" s="3" t="n">
+      <c r="AT2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="P2" s="3" t="n">
+      <c r="AU2" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q2" s="3" t="n">
+      <c r="AV2" s="4" t="n">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>2720551044</t>
         </is>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>46190.3125</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>46190.375</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="D3" s="4" t="n">
+        <v>100</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>93</v>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Khám sức khoẻ</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="AB3" s="4" t="inlineStr">
+        <is>
+          <t>0000 - Bình thường</t>
+        </is>
+      </c>
+      <c r="AC3" s="4" t="inlineStr">
+        <is>
+          <t>0000 - Bình thường</t>
+        </is>
+      </c>
+      <c r="AD3" s="4" t="inlineStr">
+        <is>
+          <t>Không</t>
+        </is>
+      </c>
+      <c r="AE3" s="4" t="inlineStr">
+        <is>
+          <t>Bình thường</t>
+        </is>
+      </c>
+      <c r="AF3" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG3" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" s="4" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Hoa</t>
+        </is>
+      </c>
+      <c r="AI3" s="4" t="n">
         <v>78</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="AJ3" s="4" t="n">
         <v>37</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="AK3" s="4" t="n">
         <v>120</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="AL3" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="AM3" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="AN3" s="4" t="n">
         <v>55</v>
       </c>
-      <c r="J3" s="3" t="n">
+      <c r="AO3" s="4" t="n">
         <v>160</v>
       </c>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n">
+      <c r="AP3" s="4" t="n"/>
+      <c r="AQ3" s="4" t="n">
         <v>72</v>
       </c>
-      <c r="M3" s="3" t="n">
+      <c r="AR3" s="4" t="n">
         <v>80</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="AS3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="O3" s="3" t="n">
+      <c r="AT3" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="P3" s="3" t="n">
+      <c r="AU3" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q3" s="3" t="n">
+      <c r="AV3" s="4" t="n">
         <v>9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q1"/>
+  <autoFilter ref="A1:AV1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -813,76 +1526,83 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>HƯỚNG DẪN</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr"/>
+      <c r="A2" s="7" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>• Mỗi dòng = 1 bệnh nhân (1 lần khám sức khoẻ).</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="7" t="inlineStr">
         <is>
           <t>• KHÔNG đổi tên các cột ở dòng tiêu đề — ứng dụng dựa vào đó để đọc dữ liệu.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>• Cột 'Mã định danh': nhập CCCD hoặc số thẻ BHYT để tìm bệnh nhân (giống ô tìm kiếm trên web). Không cần là mã định danh y tế.</t>
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>• Màu cột tiêu đề: CAM = mã định danh (bắt buộc, dùng tìm bệnh nhân); ĐỎ SẪM = bắt buộc (để trống sẽ bị lỗi); XANH = tuỳ chọn (để trống dùng giá trị mặc định).</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>• Ngày: định dạng dd/mm/yyyy, có thể kèm giờ. Để trống giờ sẽ dùng giờ mặc định.</t>
+      <c r="A6" s="7" t="inlineStr">
+        <is>
+          <t>• Cột 'Mã định danh': nhập CCCD hoặc số thẻ BHYT để tìm bệnh nhân (giống ô tìm kiếm trên web). Không cần là mã định danh y tế.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>• Cột 'BMI': để TRỐNG, ứng dụng tự tính từ cân nặng và chiều cao.</t>
+      <c r="A7" s="7" t="inlineStr">
+        <is>
+          <t>• Ngày: định dạng dd/mm/yyyy, có thể kèm giờ. Để trống giờ sẽ dùng giờ mặc định.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>• XOÁ các dòng ví dụ (in nghiêng) trước khi chạy thật.</t>
+      <c r="A8" s="7" t="inlineStr">
+        <is>
+          <t>• Cột 'BMI': để TRỐNG, ứng dụng tự tính từ cân nặng và chiều cao.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>• Di chuột vào ô tiêu đề để xem chú thích từng cột.</t>
+      <c r="A9" s="7" t="inlineStr">
+        <is>
+          <t>• XOÁ các dòng ví dụ (in nghiêng) trước khi chạy thật.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr"/>
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>• Di chuột vào ô tiêu đề để xem chú thích từng cột.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="7" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="inlineStr">
         <is>
           <t>Quy trình: Mở app → Đăng nhập → Chọn Excel → Validate → Dry-run (xem trước) → bỏ Dry-run, Limit=1 để thử 1 bệnh nhân → kiểm tra trên web → chạy toàn bộ.</t>
         </is>
